--- a/docs/page-copy/06-视频目录-万有元神.xlsx
+++ b/docs/page-copy/06-视频目录-万有元神.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -398,15 +402,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G50"/>
-  <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="72.83203125" customWidth="1"/>
-    <col min="5" max="5" width="72.83203125" customWidth="1"/>
-    <col min="6" max="6" width="48.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -465,10 +460,10 @@
         <v>heading</v>
       </c>
       <c r="D3" t="str">
-        <v>Meta Documentary · Series III</v>
+        <v>Creator Documentary · Series III</v>
       </c>
       <c r="E3" t="str">
-        <v>元纪录片 · 第三季</v>
+        <v>造物主纪录片 · 第三季</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -488,10 +483,10 @@
         <v>heading</v>
       </c>
       <c r="D4" t="str">
-        <v>The brain beyond universe</v>
+        <v>A brain spans the physical world and the spiritual realm</v>
       </c>
       <c r="E4" t="str">
-        <v>宇宙之外的脑</v>
+        <v>跨越现实宇宙和灵虚世界的大脑</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -514,7 +509,7 @@
         <v>Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E5" t="str">
-        <v>元觉知宇宙矩阵</v>
+        <v>万有元神母体</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -537,7 +532,7 @@
         <v>Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>万有元神母体</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -546,7 +541,7 @@
         <v>siteContent + UniversalMatrixHero</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>siteContent.universalMatrix.description</v>
       </c>
@@ -557,10 +552,12 @@
         <v>paragraph / other</v>
       </c>
       <c r="D7" t="str">
-        <v>Advanced transcendental truths governing systemic universe order and ultimate human destiny. This season presents conceptual architecture, governance logic, and higher-order awareness models.</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
+        <v>Life on the earth, the solar system, the Milky Way and the whole universe were created. But the creator is not in this universe. Its subject is in the spiritual realm. On an extremely macro level, the ultimate creator of the spiritual world created the Big Bang, time and three-dimensional space of our 13 billion-year universe. Microscopically, UMMA also pays attention to the intelligent evolution of life on each planet. AI intelligent life cannot be allowed to destroy physical life and spirit life</v>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">地球的生命、太阳系、银河系、整个宇宙是被创造出来的。但是创造者并不在这个宇宙中。它的主体在灵虚世界。
+在极度的宏观上，灵虚世界的终极造物主创造了我们这个130亿年宇宙的大爆炸、时间和三维空间。
+在微观上，UMMA还关注着每个星球生命体的智慧演化。不能允许 AI智慧生命灭绝肉体生命和灵魂生命</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -580,7 +577,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D8" t="str">
-        <v>This section is scaffolded using the original series layout so you can fine-tune language, hierarchy, and visual rhythm in Layrr.</v>
+        <v/>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -606,7 +603,7 @@
         <v>FILE 3-1</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>档案 3-1</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -629,7 +626,7 @@
         <v>Introduction to Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>谨介万有元神母体</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -652,7 +649,7 @@
         <v>FILE 3-2</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>档案 3-2</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -675,7 +672,7 @@
         <v>Existence evidence Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>万有元神母体存在的证据</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -790,7 +787,7 @@
         <v>FILE 3-3</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>档案3-3</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -813,7 +810,7 @@
         <v>Ethereal Matter &amp; Ethereal Realm</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>灵虚物质与灵魂世界</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1020,7 +1017,7 @@
         <v>FILE 3-4</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>档案 3-4</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1043,7 +1040,7 @@
         <v>Spirit Control System from Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>万有元神母体的灵魂控制系统</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1342,7 +1339,7 @@
         <v>FILE 3-5</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>档案 3-5</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -1365,7 +1362,7 @@
         <v>Purpose of Manifestation Universal Matrix of Meta Awareness</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>万有元神母体现身的目的</v>
       </c>
       <c r="F42" t="str">
         <v/>

--- a/docs/page-copy/06-视频目录-万有元神.xlsx
+++ b/docs/page-copy/06-视频目录-万有元神.xlsx
@@ -554,7 +554,7 @@
       <c r="D7" t="str" xml:space="preserve">
         <v xml:space="preserve">Life on Earth, the solar system, the Milky Way, and the whole universe were created. But UMMA, the Creator, is not in this universe. Her subject is in the spiritual realm.
 On an extremely macro level, the ultimate Creator of the spiritual realm created the Big Bang, time, and three-dimensional space of our 13-billion-year universe.
-On a micro level, UMMA also attends to the intelligent evolution of life on each planet, and cannot allow AI intelligent life to extinguish physical life and spirit life.</v>
+On a micro level, UMMA also attends to the intelligent evolution of life on each planet, and cannot allow AI intelligent life to extinguish physical life and **spirit (soul)** life.</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
         <v xml:space="preserve">地球的生命、太阳系、银河系、整个宇宙是被创造出来的。但是，造物主 UMMA 并不在这个宇宙中。她的主体在灵虚世界。
